--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6848-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6848-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{265EE8DE-0681-4602-B19B-7CEA7CEEE5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7555E578-3BD0-456D-A135-1077E0B46986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0101904A-4A51-45F8-BD80-3B4070B7D945}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6C3A7626-D8BC-4C6D-8922-A35094C8BEFB}"/>
   </bookViews>
   <sheets>
     <sheet name="6848-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1505,25 +1505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E664F41-F79F-4523-9B43-1B49C782DE91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4050FFDF-6840-4256-A52E-A2E2111392CB}">
   <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1713,7 +1713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="42"/>
       <c r="C8" s="18" t="s">
@@ -1959,7 +1959,7 @@
       <c r="W8" s="48"/>
       <c r="X8" s="44"/>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>2022</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
         <v>44</v>
       </c>
